--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1771,57 +1771,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94912306</v>
+        <v>136782785</v>
       </c>
       <c r="B11" t="n">
-        <v>58327</v>
+        <v>58448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grenforsens NR, Tuna, Mpd 754 m SW, Mpd</t>
+          <t>Tunbyn, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>614589</v>
+        <v>614602</v>
       </c>
       <c r="R11" t="n">
-        <v>6909911</v>
+        <v>6909977</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1848,22 +1844,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-07-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-07-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1878,70 +1874,70 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Thomas Olsson</t>
+          <t>Eva Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Thomas Olsson</t>
+          <t>Eva Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94912306</t>
+          <t>https://artportalen.se/Sighting/136782785</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99641214</v>
+        <v>136782773</v>
       </c>
       <c r="B12" t="n">
-        <v>58327</v>
+        <v>58443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Krokforsen stigen, Mpd</t>
+          <t>Tunbyn, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>614626</v>
+        <v>614602</v>
       </c>
       <c r="R12" t="n">
-        <v>6909906</v>
+        <v>6909977</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1968,22 +1964,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-04-03</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-04-03</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1998,18 +1994,382 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Lagerborg</t>
+          <t>Eva Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Lagerborg</t>
+          <t>Eva Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136782773</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>94912306</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Grenforsens NR, Tuna, Mpd 754 m SW, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>614589</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6909911</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-07-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-07-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Thomas Olsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Thomas Olsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94912306</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>99641214</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Krokforsen stigen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>614626</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6909906</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-04-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-04-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maria Lagerborg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maria Lagerborg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/99641214</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136782791</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58629</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tunbyn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>614602</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6909977</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Eva Olsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Eva Olsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136782791</t>
         </is>
       </c>
     </row>
@@ -2026,6 +2386,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1774,7 +1774,7 @@
         <v>136782785</v>
       </c>
       <c r="B11" t="n">
-        <v>58448</v>
+        <v>58461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>136782773</v>
       </c>
       <c r="B12" t="n">
-        <v>58443</v>
+        <v>58456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>136782791</v>
       </c>
       <c r="B15" t="n">
-        <v>58629</v>
+        <v>58642</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1774,7 +1774,7 @@
         <v>136782785</v>
       </c>
       <c r="B11" t="n">
-        <v>58461</v>
+        <v>58463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>136782773</v>
       </c>
       <c r="B12" t="n">
-        <v>58456</v>
+        <v>58458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>136782791</v>
       </c>
       <c r="B15" t="n">
-        <v>58642</v>
+        <v>58644</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1802,11 +1802,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1922,11 +1918,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2286,11 +2278,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1774,7 +1774,7 @@
         <v>136782785</v>
       </c>
       <c r="B11" t="n">
-        <v>58463</v>
+        <v>58473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>136782773</v>
       </c>
       <c r="B12" t="n">
-        <v>58458</v>
+        <v>58468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>136782791</v>
       </c>
       <c r="B15" t="n">
-        <v>58644</v>
+        <v>58654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1774,7 +1774,7 @@
         <v>136782785</v>
       </c>
       <c r="B11" t="n">
-        <v>58473</v>
+        <v>58474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>136782773</v>
       </c>
       <c r="B12" t="n">
-        <v>58468</v>
+        <v>58469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>136782791</v>
       </c>
       <c r="B15" t="n">
-        <v>58654</v>
+        <v>58656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 58518-2022 artfynd.xlsx
+++ b/artfynd/A 58518-2022 artfynd.xlsx
@@ -1774,7 +1774,7 @@
         <v>136782785</v>
       </c>
       <c r="B11" t="n">
-        <v>58474</v>
+        <v>58476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>136782773</v>
       </c>
       <c r="B12" t="n">
-        <v>58469</v>
+        <v>58471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>136782791</v>
       </c>
       <c r="B15" t="n">
-        <v>58656</v>
+        <v>58658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
